--- a/spreadsheets/HRDataset_v14.xlsx
+++ b/spreadsheets/HRDataset_v14.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b827e86ed6b30f2b/Documents/College/Y4S2/INFO 3401/Portfolio Project 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="8_{C14E98F4-E85A-4FDA-9E6A-B6ED462181A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B4C827A-F682-4177-80C9-5FFF67D66989}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="8_{C14E98F4-E85A-4FDA-9E6A-B6ED462181A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7545FB5-A455-484D-BF36-08027C8FCE5B}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{75324C80-B1E6-4537-B4EF-CCD61596DD0A}"/>
+    <workbookView xWindow="43425" yWindow="5025" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{75324C80-B1E6-4537-B4EF-CCD61596DD0A}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -24,10 +24,23 @@
     <definedName name="Total_Employees">'Attrition Analysis'!$B$11</definedName>
     <definedName name="Total_Terminations">'Attrition Analysis'!$C$11</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="35" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1935,7 +1948,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="34" x14ac:knownFonts="1">
     <font>
@@ -2677,7 +2690,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2688,49 +2701,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="18" fillId="35" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="18" fillId="35" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="37" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="29" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="31" fillId="41" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="42" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2740,7 +2732,27 @@
     <xf numFmtId="0" fontId="19" fillId="42" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="41" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -2791,30 +2803,6 @@
   <dxfs count="27">
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="3" tint="0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -2830,73 +2818,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="168" formatCode="0.0%"/>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="0" tint="-0.14999847407452621"/>
@@ -2978,13 +2900,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color theme="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <top style="medium">
           <color theme="1"/>
         </top>
@@ -3007,7 +2922,62 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="168" formatCode="0.0%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="3" tint="0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="0" tint="-0.14999847407452621"/>
@@ -3075,7 +3045,11 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -3086,6 +3060,11 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.249977111117893"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3104,7 +3083,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="168" formatCode="0.0%"/>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
     </dxf>
     <dxf>
       <font>
@@ -3161,6 +3140,39 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.249977111117893"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -6094,6 +6106,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Ryan Fish" refreshedDate="46136.836408564814" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="311" xr:uid="{756DCE67-243A-4D07-88EC-0C022787A2B5}">
   <cacheSource type="worksheet">
@@ -18089,7 +18105,272 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EFECEFA3-7202-44E8-A82E-95C274FB672A}" name="PivotTable15" cacheId="35" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10029A5B-7BBE-4784-8A4B-23A6C0BB6B18}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="F3:G22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="36">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="19">
+        <item x="4"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="14"/>
+        <item x="17"/>
+        <item x="2"/>
+        <item x="8"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="12"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="23"/>
+  </rowFields>
+  <rowItems count="19">
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of EmpID" fld="1" subtotal="count" baseField="23" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0E46CBB2-19AB-4B9F-96ED-9811D83AAE59}" name="PivotTable13" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="36">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="7">
+        <item x="3"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="25"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Count of EmpID" fld="1" subtotal="count" baseField="25" baseItem="0"/>
+    <dataField name="Sum of Termd" fld="10" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EFECEFA3-7202-44E8-A82E-95C274FB672A}" name="PivotTable15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="I3:K25" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="36">
     <pivotField showAll="0"/>
@@ -18261,271 +18542,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10029A5B-7BBE-4784-8A4B-23A6C0BB6B18}" name="PivotTable14" cacheId="35" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="F3:G22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="36">
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="19">
-        <item x="4"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="14"/>
-        <item x="17"/>
-        <item x="2"/>
-        <item x="8"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="12"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="23"/>
-  </rowFields>
-  <rowItems count="19">
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of EmpID" fld="1" subtotal="count" baseField="23" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0E46CBB2-19AB-4B9F-96ED-9811D83AAE59}" name="PivotTable13" cacheId="35" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:C10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="36">
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="7">
-        <item x="3"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="25"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Count of EmpID" fld="1" subtotal="count" baseField="25" baseItem="0"/>
-    <dataField name="Sum of Termd" fld="10" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{871BA7C9-7D9C-4542-A28B-252F2A7F7905}" name="Table1" displayName="Table1" ref="A1:AJ312" totalsRowShown="0">
   <autoFilter ref="A1:AJ312" xr:uid="{871BA7C9-7D9C-4542-A28B-252F2A7F7905}"/>
@@ -18572,45 +18588,45 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{24C328B1-0BC1-4AC3-9C20-C27DFE9862D2}" name="Table2" displayName="Table2" ref="A2:C37" totalsRowShown="0" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{24C328B1-0BC1-4AC3-9C20-C27DFE9862D2}" name="Table2" displayName="Table2" ref="A2:C37" totalsRowShown="0" dataDxfId="23">
   <autoFilter ref="A2:C37" xr:uid="{24C328B1-0BC1-4AC3-9C20-C27DFE9862D2}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D0097888-EAFF-4A94-BB5A-B513485D96BB}" name="Feature" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{8D96037E-ECCA-40DE-9F8B-6E75DCC95164}" name="Description" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{FAB20506-5886-402A-9580-EC5B793629D1}" name="DataType" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{D0097888-EAFF-4A94-BB5A-B513485D96BB}" name="Feature" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{8D96037E-ECCA-40DE-9F8B-6E75DCC95164}" name="Description" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{FAB20506-5886-402A-9580-EC5B793629D1}" name="DataType" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B4B6B598-4DA5-40D6-994C-DE3668380435}" name="Table3" displayName="Table3" ref="A4:E11" totalsRowShown="0" headerRowDxfId="2" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B4B6B598-4DA5-40D6-994C-DE3668380435}" name="Table3" displayName="Table3" ref="A4:E11" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="A4:E11" xr:uid="{B4B6B598-4DA5-40D6-994C-DE3668380435}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:E11">
     <sortCondition descending="1" ref="E4:E11"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3D8513A8-2D77-4A62-B57A-FE841938667B}" name="Department" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{AE92DAEF-60FB-46E4-847B-7C21150C8596}" name="Total Emp" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{F69B4EBB-CBDE-45AF-B0F7-1F072F7F0F5E}" name="Terminated" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{73A7A6CA-3669-4006-AAD6-5BAEB250F695}" name="Active" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{1A37DE88-4224-4301-A6C9-7FEA23D43CF8}" name="Attrition Rate" dataDxfId="15" dataCellStyle="Percent"/>
+    <tableColumn id="1" xr3:uid="{3D8513A8-2D77-4A62-B57A-FE841938667B}" name="Department" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{AE92DAEF-60FB-46E4-847B-7C21150C8596}" name="Total Emp" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{F69B4EBB-CBDE-45AF-B0F7-1F072F7F0F5E}" name="Terminated" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{73A7A6CA-3669-4006-AAD6-5BAEB250F695}" name="Active" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{1A37DE88-4224-4301-A6C9-7FEA23D43CF8}" name="Attrition Rate" dataDxfId="13" dataCellStyle="Percent"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8837DEF6-4CF9-4978-987C-46E92189D4C3}" name="Table6" displayName="Table6" ref="G4:I14" totalsRowShown="0" headerRowDxfId="1" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8837DEF6-4CF9-4978-987C-46E92189D4C3}" name="Table6" displayName="Table6" ref="G4:I14" totalsRowShown="0" headerRowDxfId="12" tableBorderDxfId="11">
   <autoFilter ref="G4:I14" xr:uid="{8837DEF6-4CF9-4978-987C-46E92189D4C3}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{14FBA231-3221-4FD2-989C-CF8A2D2C1D92}" name="Reason" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{14FBA231-3221-4FD2-989C-CF8A2D2C1D92}" name="Reason" dataDxfId="10">
       <calculatedColumnFormula>INDEX('Pivot Tables'!F5:F14,1,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{30C664B1-E6ED-4943-BD79-7617F84C7023}" name="Count" dataDxfId="11">
+    <tableColumn id="2" xr3:uid="{30C664B1-E6ED-4943-BD79-7617F84C7023}" name="Count" dataDxfId="9">
       <calculatedColumnFormula>VLOOKUP(G5,'Pivot Tables'!F4:G21,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1B5DEE34-61E7-403B-BF24-4F0F481CA5E0}" name="% Leave" dataDxfId="10" dataCellStyle="Percent">
+    <tableColumn id="3" xr3:uid="{1B5DEE34-61E7-403B-BF24-4F0F481CA5E0}" name="% Leave" dataDxfId="8" dataCellStyle="Percent">
       <calculatedColumnFormula>H5/Total_Terminations</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -18619,15 +18635,15 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{D745049F-A9AB-4378-B91F-E40B745F04F3}" name="Table7" displayName="Table7" ref="K4:N13" totalsRowShown="0" headerRowDxfId="0" dataDxfId="3" headerRowBorderDxfId="8" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{D745049F-A9AB-4378-B91F-E40B745F04F3}" name="Table7" displayName="Table7" ref="K4:N13" totalsRowShown="0" headerRowDxfId="7" dataDxfId="5" headerRowBorderDxfId="6" tableBorderDxfId="4">
   <autoFilter ref="K4:N13" xr:uid="{D745049F-A9AB-4378-B91F-E40B745F04F3}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{EE9FB931-7E21-49F6-8A1A-ED57AFC2FBE4}" name="Manager" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{B46AAC90-D4E0-4CAD-A532-6E2190710BD8}" name="Team Size" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{EE9FB931-7E21-49F6-8A1A-ED57AFC2FBE4}" name="Manager" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{B46AAC90-D4E0-4CAD-A532-6E2190710BD8}" name="Team Size" dataDxfId="2">
       <calculatedColumnFormula>VLOOKUP(K5,'Pivot Tables'!$I$4:$K$24,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BB1B856C-8CD5-4E5C-949D-58137BEF4BB5}" name="Team Termd" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{7B6246AB-5716-4005-86E0-C7AF43E083D4}" name="Attrition Rate" dataDxfId="4" dataCellStyle="Percent">
+    <tableColumn id="3" xr3:uid="{BB1B856C-8CD5-4E5C-949D-58137BEF4BB5}" name="Team Termd" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{7B6246AB-5716-4005-86E0-C7AF43E083D4}" name="Attrition Rate" dataDxfId="0" dataCellStyle="Percent">
       <calculatedColumnFormula>M5/L5</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -18955,16 +18971,16 @@
   <dimension ref="A1:V39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="18"/>
+    <col min="1" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="21" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:16" s="29" customFormat="1" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="22" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:16" s="22" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" s="18" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:16" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="24" t="s">
         <v>1</v>
       </c>
@@ -18981,222 +18997,230 @@
         <v>4</v>
       </c>
       <c r="O4" s="24"/>
-      <c r="P4" s="27"/>
+      <c r="P4" s="20"/>
     </row>
-    <row r="5" spans="1:16" s="22" customFormat="1" ht="24" x14ac:dyDescent="0.4">
-      <c r="B5" s="23">
+    <row r="5" spans="1:16" s="18" customFormat="1" ht="24" x14ac:dyDescent="0.4">
+      <c r="B5" s="30">
         <v>311</v>
       </c>
-      <c r="C5" s="23"/>
-      <c r="F5" s="25">
+      <c r="C5" s="30"/>
+      <c r="F5" s="31">
         <v>207</v>
       </c>
-      <c r="G5" s="25"/>
-      <c r="J5" s="28">
+      <c r="G5" s="31"/>
+      <c r="J5" s="32">
         <v>104</v>
       </c>
-      <c r="K5" s="28"/>
-      <c r="L5" s="26"/>
-      <c r="N5" s="29">
+      <c r="K5" s="32"/>
+      <c r="L5" s="19"/>
+      <c r="N5" s="33">
         <v>0.33400000000000002</v>
       </c>
-      <c r="O5" s="29"/>
+      <c r="O5" s="33"/>
     </row>
-    <row r="6" spans="1:16" s="22" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:16" s="22" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:1" s="30" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="30" t="s">
+    <row r="6" spans="1:16" s="18" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:16" s="18" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:1" s="25" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="25" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="33" t="s">
+      <c r="A33" s="26" t="s">
         <v>561</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="31" t="s">
+      <c r="B33" s="27"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31"/>
-      <c r="P33" s="31"/>
-      <c r="Q33" s="31"/>
-      <c r="R33" s="31"/>
-      <c r="S33" s="31"/>
-      <c r="T33" s="31"/>
-      <c r="U33" s="31"/>
-      <c r="V33" s="36"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="21"/>
+      <c r="O33" s="21"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="21"/>
+      <c r="R33" s="21"/>
+      <c r="S33" s="21"/>
+      <c r="T33" s="21"/>
+      <c r="U33" s="21"/>
+      <c r="V33" s="23"/>
     </row>
     <row r="34" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="33" t="s">
+      <c r="A34" s="26" t="s">
         <v>562</v>
       </c>
-      <c r="B34" s="34"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="32" t="s">
+      <c r="B34" s="27"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
-      <c r="L34" s="32"/>
-      <c r="M34" s="32"/>
-      <c r="N34" s="32"/>
-      <c r="O34" s="32"/>
-      <c r="P34" s="32"/>
-      <c r="Q34" s="32"/>
-      <c r="R34" s="32"/>
-      <c r="S34" s="32"/>
-      <c r="T34" s="32"/>
-      <c r="U34" s="32"/>
-      <c r="V34" s="36"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22"/>
+      <c r="R34" s="22"/>
+      <c r="S34" s="22"/>
+      <c r="T34" s="22"/>
+      <c r="U34" s="22"/>
+      <c r="V34" s="23"/>
     </row>
     <row r="35" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="33" t="s">
+      <c r="A35" s="26" t="s">
         <v>563</v>
       </c>
-      <c r="B35" s="34"/>
-      <c r="C35" s="35"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32"/>
-      <c r="J35" s="32"/>
-      <c r="K35" s="32"/>
-      <c r="L35" s="32"/>
-      <c r="M35" s="32"/>
-      <c r="N35" s="32"/>
-      <c r="O35" s="32"/>
-      <c r="P35" s="32"/>
-      <c r="Q35" s="32"/>
-      <c r="R35" s="32"/>
-      <c r="S35" s="32"/>
-      <c r="T35" s="32"/>
-      <c r="U35" s="32"/>
-      <c r="V35" s="36"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22"/>
+      <c r="R35" s="22"/>
+      <c r="S35" s="22"/>
+      <c r="T35" s="22"/>
+      <c r="U35" s="22"/>
+      <c r="V35" s="23"/>
     </row>
     <row r="36" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="33" t="s">
+      <c r="A36" s="26" t="s">
         <v>563</v>
       </c>
-      <c r="B36" s="34"/>
-      <c r="C36" s="35"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="32"/>
-      <c r="N36" s="32"/>
-      <c r="O36" s="32"/>
-      <c r="P36" s="32"/>
-      <c r="Q36" s="32"/>
-      <c r="R36" s="32"/>
-      <c r="S36" s="32"/>
-      <c r="T36" s="32"/>
-      <c r="U36" s="32"/>
-      <c r="V36" s="36"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22"/>
+      <c r="R36" s="22"/>
+      <c r="S36" s="22"/>
+      <c r="T36" s="22"/>
+      <c r="U36" s="22"/>
+      <c r="V36" s="23"/>
     </row>
     <row r="37" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="33" t="s">
+      <c r="A37" s="26" t="s">
         <v>563</v>
       </c>
-      <c r="B37" s="34"/>
-      <c r="C37" s="35"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="32"/>
-      <c r="J37" s="32"/>
-      <c r="K37" s="32"/>
-      <c r="L37" s="32"/>
-      <c r="M37" s="32"/>
-      <c r="N37" s="32"/>
-      <c r="O37" s="32"/>
-      <c r="P37" s="32"/>
-      <c r="Q37" s="32"/>
-      <c r="R37" s="32"/>
-      <c r="S37" s="32"/>
-      <c r="T37" s="32"/>
-      <c r="U37" s="32"/>
-      <c r="V37" s="36"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="22"/>
+      <c r="R37" s="22"/>
+      <c r="S37" s="22"/>
+      <c r="T37" s="22"/>
+      <c r="U37" s="22"/>
+      <c r="V37" s="23"/>
     </row>
     <row r="38" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="33" t="s">
+      <c r="A38" s="26" t="s">
         <v>563</v>
       </c>
-      <c r="B38" s="34"/>
-      <c r="C38" s="35"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="32"/>
-      <c r="J38" s="32"/>
-      <c r="K38" s="32"/>
-      <c r="L38" s="32"/>
-      <c r="M38" s="32"/>
-      <c r="N38" s="32"/>
-      <c r="O38" s="32"/>
-      <c r="P38" s="32"/>
-      <c r="Q38" s="32"/>
-      <c r="R38" s="32"/>
-      <c r="S38" s="32"/>
-      <c r="T38" s="32"/>
-      <c r="U38" s="32"/>
-      <c r="V38" s="36"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="22"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="22"/>
+      <c r="R38" s="22"/>
+      <c r="S38" s="22"/>
+      <c r="T38" s="22"/>
+      <c r="U38" s="22"/>
+      <c r="V38" s="23"/>
     </row>
     <row r="39" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="33" t="s">
+      <c r="A39" s="26" t="s">
         <v>563</v>
       </c>
-      <c r="B39" s="34"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="32"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="32"/>
-      <c r="L39" s="32"/>
-      <c r="M39" s="32"/>
-      <c r="N39" s="32"/>
-      <c r="O39" s="32"/>
-      <c r="P39" s="32"/>
-      <c r="Q39" s="32"/>
-      <c r="R39" s="32"/>
-      <c r="S39" s="32"/>
-      <c r="T39" s="32"/>
-      <c r="U39" s="32"/>
-      <c r="V39" s="36"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="22"/>
+      <c r="N39" s="22"/>
+      <c r="O39" s="22"/>
+      <c r="P39" s="22"/>
+      <c r="Q39" s="22"/>
+      <c r="R39" s="22"/>
+      <c r="S39" s="22"/>
+      <c r="T39" s="22"/>
+      <c r="U39" s="22"/>
+      <c r="V39" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:XFD1"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="J4:K4"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="A32:XFD32"/>
     <mergeCell ref="A39:C39"/>
@@ -19206,14 +19230,6 @@
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A1:XFD1"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="J4:K4"/>
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -53371,18 +53387,18 @@
   <dimension ref="A3:K25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="18"/>
-    <col min="5" max="5" width="3.5703125" style="18" customWidth="1"/>
-    <col min="6" max="6" width="28.28515625" style="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.5703125" style="18" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" style="18" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="18"/>
+    <col min="1" max="1" width="19.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="15"/>
+    <col min="5" max="5" width="3.5703125" style="15" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.5703125" style="15" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -53395,7 +53411,7 @@
       <c r="C3" t="s">
         <v>546</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>547</v>
       </c>
       <c r="F3" s="6" t="s">
@@ -53418,29 +53434,29 @@
       <c r="A4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4">
         <v>209</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4">
         <v>83</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <f>GETPIVOTDATA("Sum of Termd",$A$3,"Department","Production       ")/GETPIVOTDATA("Sum of Termd",$A$3)</f>
         <v>0.79807692307692313</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4">
         <v>207</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4">
         <v>21</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4">
         <v>13</v>
       </c>
     </row>
@@ -53448,29 +53464,29 @@
       <c r="A5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5">
         <v>50</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5">
         <v>10</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <f>GETPIVOTDATA("Sum of Termd",$A$3,"Department","IT/IS")/GETPIVOTDATA("Sum of Termd",$A$3)</f>
         <v>9.6153846153846159E-2</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5">
         <v>20</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5">
         <v>21</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5">
         <v>13</v>
       </c>
     </row>
@@ -53478,29 +53494,29 @@
       <c r="A6" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6">
         <v>31</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <f>GETPIVOTDATA("Sum of Termd",$A$3,"Department","Sales")/GETPIVOTDATA("Sum of Termd",$A$3)</f>
         <v>4.807692307692308E-2</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6">
         <v>14</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6">
         <v>22</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6">
         <v>12</v>
       </c>
     </row>
@@ -53508,29 +53524,29 @@
       <c r="A7" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7">
         <v>11</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7">
         <v>4</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <f>GETPIVOTDATA("Sum of Termd",$A$3,"Department","Software Engineering")/GETPIVOTDATA("Sum of Termd",$A$3)</f>
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7">
         <v>11</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7">
         <v>22</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7">
         <v>9</v>
       </c>
     </row>
@@ -53538,29 +53554,29 @@
       <c r="A8" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8">
         <v>9</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8">
         <v>2</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <f>GETPIVOTDATA("Sum of Termd",$A$3,"Department","Admin Offices")/GETPIVOTDATA("Sum of Termd",$A$3)</f>
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8">
         <v>9</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8">
         <v>17</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8">
         <v>8</v>
       </c>
     </row>
@@ -53568,29 +53584,29 @@
       <c r="A9" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="B9" s="8">
-        <v>1</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0</v>
-      </c>
-      <c r="D9" s="10">
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9">
         <f>GETPIVOTDATA("Sum of Termd",$A$3,"Department","Executive Office")/GETPIVOTDATA("Sum of Termd",$A$3)</f>
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9">
         <v>8</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9">
         <v>22</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9">
         <v>8</v>
       </c>
     </row>
@@ -53598,26 +53614,26 @@
       <c r="A10" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10">
         <v>311</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10">
         <v>104</v>
       </c>
-      <c r="D10" s="20"/>
+      <c r="D10" s="17"/>
       <c r="F10" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10">
         <v>7</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10">
         <v>21</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10">
         <v>6</v>
       </c>
     </row>
@@ -53625,16 +53641,16 @@
       <c r="F11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11">
         <v>5</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11">
         <v>22</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11">
         <v>6</v>
       </c>
     </row>
@@ -53642,16 +53658,16 @@
       <c r="F12" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12">
         <v>5</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12">
         <v>22</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12">
         <v>6</v>
       </c>
     </row>
@@ -53659,16 +53675,16 @@
       <c r="F13" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13">
         <v>4</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13">
         <v>19</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13">
         <v>6</v>
       </c>
     </row>
@@ -53676,16 +53692,16 @@
       <c r="F14" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14">
         <v>4</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14">
         <v>21</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14">
         <v>5</v>
       </c>
     </row>
@@ -53693,16 +53709,16 @@
       <c r="F15" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15">
         <v>4</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15">
         <v>9</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15">
         <v>3</v>
       </c>
     </row>
@@ -53710,16 +53726,16 @@
       <c r="F16" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16">
         <v>4</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16">
         <v>14</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16">
         <v>3</v>
       </c>
     </row>
@@ -53727,16 +53743,16 @@
       <c r="F17" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17">
         <v>3</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17">
         <v>7</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17">
         <v>2</v>
       </c>
     </row>
@@ -53744,16 +53760,16 @@
       <c r="F18" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18">
         <v>3</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18">
         <v>14</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18">
         <v>1</v>
       </c>
     </row>
@@ -53761,16 +53777,16 @@
       <c r="F19" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19">
         <v>1</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19">
         <v>7</v>
       </c>
-      <c r="K19" s="8">
+      <c r="K19">
         <v>1</v>
       </c>
     </row>
@@ -53778,16 +53794,16 @@
       <c r="F20" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20">
         <v>1</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20">
         <v>13</v>
       </c>
-      <c r="K20" s="8">
+      <c r="K20">
         <v>1</v>
       </c>
     </row>
@@ -53795,16 +53811,16 @@
       <c r="F21" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21">
         <v>1</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21">
         <v>3</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21">
         <v>1</v>
       </c>
     </row>
@@ -53812,16 +53828,16 @@
       <c r="F22" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22">
         <v>311</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22">
         <v>8</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22">
         <v>0</v>
       </c>
     </row>
@@ -53829,10 +53845,10 @@
       <c r="I23" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J23">
         <v>4</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23">
         <v>0</v>
       </c>
     </row>
@@ -53840,10 +53856,10 @@
       <c r="I24" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J24">
         <v>2</v>
       </c>
-      <c r="K24" s="8">
+      <c r="K24">
         <v>0</v>
       </c>
     </row>
@@ -53851,10 +53867,10 @@
       <c r="I25" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="J25" s="8">
+      <c r="J25">
         <v>311</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25">
         <v>104</v>
       </c>
     </row>
@@ -53868,91 +53884,91 @@
   <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" style="18" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="18" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" style="18" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="18"/>
-    <col min="5" max="5" width="14.42578125" style="18" customWidth="1"/>
-    <col min="6" max="6" width="2" style="18" customWidth="1"/>
-    <col min="7" max="7" width="29.5703125" style="19" customWidth="1"/>
-    <col min="8" max="9" width="11" style="18" customWidth="1"/>
-    <col min="10" max="10" width="1.85546875" style="18" customWidth="1"/>
-    <col min="11" max="11" width="27.28515625" style="18" customWidth="1"/>
-    <col min="12" max="12" width="12" style="18" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" style="18" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="18" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="18"/>
+    <col min="1" max="1" width="13.42578125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="15" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" style="15" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="15"/>
+    <col min="5" max="5" width="14.42578125" style="15" customWidth="1"/>
+    <col min="6" max="6" width="2" style="15" customWidth="1"/>
+    <col min="7" max="7" width="29.5703125" style="16" customWidth="1"/>
+    <col min="8" max="9" width="11" style="15" customWidth="1"/>
+    <col min="10" max="10" width="1.85546875" style="15" customWidth="1"/>
+    <col min="11" max="11" width="27.28515625" style="15" customWidth="1"/>
+    <col min="12" max="12" width="12" style="15" customWidth="1"/>
+    <col min="13" max="13" width="14.140625" style="15" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="15" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="14" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:14" s="34" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="35" t="s">
         <v>549</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="G3" s="15" t="s">
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="G3" s="35" t="s">
         <v>552</v>
       </c>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="15" t="s">
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="35" t="s">
         <v>556</v>
       </c>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="13" t="s">
         <v>470</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="13" t="s">
         <v>550</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="13" t="s">
         <v>551</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="13" t="s">
         <v>553</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="13" t="s">
         <v>554</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="13" t="s">
         <v>555</v>
       </c>
-      <c r="J4" s="19"/>
-      <c r="K4" s="17" t="s">
+      <c r="J4" s="16"/>
+      <c r="K4" s="14" t="s">
         <v>557</v>
       </c>
-      <c r="L4" s="17" t="s">
+      <c r="L4" s="14" t="s">
         <v>558</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="14" t="s">
         <v>560</v>
       </c>
-      <c r="N4" s="17" t="s">
+      <c r="N4" s="14" t="s">
         <v>551</v>
       </c>
     </row>
@@ -53970,11 +53986,11 @@
         <v>83</v>
       </c>
       <c r="D5" s="2">
-        <f>B5-C5</f>
+        <f t="shared" ref="D5:D10" si="0">B5-C5</f>
         <v>126</v>
       </c>
-      <c r="E5" s="11">
-        <f>C5/B5</f>
+      <c r="E5" s="10">
+        <f t="shared" ref="E5:E10" si="1">C5/B5</f>
         <v>0.39712918660287083</v>
       </c>
       <c r="G5" s="2" t="str">
@@ -53985,25 +54001,25 @@
         <f>VLOOKUP(G5,'Pivot Tables'!F4:G21,2,FALSE)</f>
         <v>20</v>
       </c>
-      <c r="I5" s="11">
-        <f>H5/Total_Terminations</f>
+      <c r="I5" s="10">
+        <f t="shared" ref="I5:I14" si="2">H5/Total_Terminations</f>
         <v>0.19230769230769232</v>
       </c>
-      <c r="J5" s="19"/>
-      <c r="K5" s="12" t="str">
+      <c r="J5" s="16"/>
+      <c r="K5" s="11" t="str">
         <f>INDEX('Pivot Tables'!I4:I24,1,1)</f>
         <v>Amy Dunn</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="11">
         <f>VLOOKUP(K5,'Pivot Tables'!$I$4:$K$24,2,FALSE)</f>
         <v>21</v>
       </c>
-      <c r="M5" s="12">
+      <c r="M5" s="11">
         <f>VLOOKUP('Attrition Analysis'!K5,'Pivot Tables'!$I$4:$K$24,3,FALSE)</f>
         <v>13</v>
       </c>
-      <c r="N5" s="13">
-        <f>M5/L5</f>
+      <c r="N5" s="12">
+        <f t="shared" ref="N5:N13" si="3">M5/L5</f>
         <v>0.61904761904761907</v>
       </c>
     </row>
@@ -54021,11 +54037,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="2">
-        <f>B6-C6</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E6" s="11">
-        <f>C6/B6</f>
+      <c r="E6" s="10">
+        <f t="shared" si="1"/>
         <v>0.36363636363636365</v>
       </c>
       <c r="G6" s="2" t="str">
@@ -54036,11 +54052,11 @@
         <f>VLOOKUP(G6,'Pivot Tables'!F5:G22,2,FALSE)</f>
         <v>14</v>
       </c>
-      <c r="I6" s="11">
-        <f>H6/Total_Terminations</f>
+      <c r="I6" s="10">
+        <f t="shared" si="2"/>
         <v>0.13461538461538461</v>
       </c>
-      <c r="J6" s="19"/>
+      <c r="J6" s="16"/>
       <c r="K6" s="2" t="str">
         <f>INDEX('Pivot Tables'!I6:I26,1,1)</f>
         <v>Kissy Sullivan</v>
@@ -54053,8 +54069,8 @@
         <f>VLOOKUP('Attrition Analysis'!K6,'Pivot Tables'!$I$4:$K$24,3,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="N6" s="11">
-        <f>M6/L6</f>
+      <c r="N6" s="10">
+        <f t="shared" si="3"/>
         <v>0.54545454545454541</v>
       </c>
     </row>
@@ -54072,11 +54088,11 @@
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <f>B7-C7</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E7" s="11">
-        <f>C7/B7</f>
+      <c r="E7" s="10">
+        <f t="shared" si="1"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="G7" s="2" t="str">
@@ -54087,25 +54103,25 @@
         <f>VLOOKUP(G7,'Pivot Tables'!F6:G23,2,FALSE)</f>
         <v>11</v>
       </c>
-      <c r="I7" s="11">
-        <f>H7/Total_Terminations</f>
+      <c r="I7" s="10">
+        <f t="shared" si="2"/>
         <v>0.10576923076923077</v>
       </c>
-      <c r="J7" s="19"/>
-      <c r="K7" s="12" t="str">
+      <c r="J7" s="16"/>
+      <c r="K7" s="11" t="str">
         <f>INDEX('Pivot Tables'!I8:I28,1,1)</f>
         <v>Simon Roup</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="11">
         <f>VLOOKUP(K7,'Pivot Tables'!$I$4:$K$24,2,FALSE)</f>
         <v>17</v>
       </c>
-      <c r="M7" s="12">
+      <c r="M7" s="11">
         <f>VLOOKUP('Attrition Analysis'!K8,'Pivot Tables'!$I$4:$K$24,3,FALSE)</f>
         <v>9</v>
       </c>
-      <c r="N7" s="13">
-        <f>M7/L7</f>
+      <c r="N7" s="12">
+        <f t="shared" si="3"/>
         <v>0.52941176470588236</v>
       </c>
     </row>
@@ -54123,11 +54139,11 @@
         <v>10</v>
       </c>
       <c r="D8" s="2">
-        <f>B8-C8</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="E8" s="11">
-        <f>C8/B8</f>
+      <c r="E8" s="10">
+        <f t="shared" si="1"/>
         <v>0.2</v>
       </c>
       <c r="G8" s="2" t="str">
@@ -54138,11 +54154,11 @@
         <f>VLOOKUP(G8,'Pivot Tables'!F7:G24,2,FALSE)</f>
         <v>9</v>
       </c>
-      <c r="I8" s="11">
-        <f>H8/Total_Terminations</f>
+      <c r="I8" s="10">
+        <f t="shared" si="2"/>
         <v>8.6538461538461536E-2</v>
       </c>
-      <c r="J8" s="19"/>
+      <c r="J8" s="16"/>
       <c r="K8" s="2" t="str">
         <f>INDEX('Pivot Tables'!I7:I27,1,1)</f>
         <v>Michael Albert</v>
@@ -54155,8 +54171,8 @@
         <f>VLOOKUP('Attrition Analysis'!K7,'Pivot Tables'!$I$4:$K$24,3,FALSE)</f>
         <v>8</v>
       </c>
-      <c r="N8" s="11">
-        <f>M8/L8</f>
+      <c r="N8" s="10">
+        <f t="shared" si="3"/>
         <v>0.36363636363636365</v>
       </c>
     </row>
@@ -54174,11 +54190,11 @@
         <v>5</v>
       </c>
       <c r="D9" s="2">
-        <f>B9-C9</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="E9" s="11">
-        <f>C9/B9</f>
+      <c r="E9" s="10">
+        <f t="shared" si="1"/>
         <v>0.16129032258064516</v>
       </c>
       <c r="G9" s="2" t="str">
@@ -54189,24 +54205,24 @@
         <f>VLOOKUP(G9,'Pivot Tables'!F8:G25,2,FALSE)</f>
         <v>8</v>
       </c>
-      <c r="I9" s="11">
-        <f>H9/Total_Terminations</f>
+      <c r="I9" s="10">
+        <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="K9" s="12" t="str">
+      <c r="K9" s="11" t="str">
         <f>INDEX('Pivot Tables'!I9:I29,1,1)</f>
         <v>Elijiah Gray</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="11">
         <f>VLOOKUP(K9,'Pivot Tables'!$I$4:$K$24,2,FALSE)</f>
         <v>22</v>
       </c>
-      <c r="M9" s="12">
+      <c r="M9" s="11">
         <f>VLOOKUP('Attrition Analysis'!K9,'Pivot Tables'!$I$4:$K$24,3,FALSE)</f>
         <v>8</v>
       </c>
-      <c r="N9" s="13">
-        <f>M9/L9</f>
+      <c r="N9" s="12">
+        <f t="shared" si="3"/>
         <v>0.36363636363636365</v>
       </c>
     </row>
@@ -54224,11 +54240,11 @@
         <v>0</v>
       </c>
       <c r="D10" s="2">
-        <f>B10-C10</f>
-        <v>1</v>
-      </c>
-      <c r="E10" s="11">
-        <f>C10/B10</f>
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E10" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G10" s="2" t="str">
@@ -54239,8 +54255,8 @@
         <f>VLOOKUP(G10,'Pivot Tables'!F9:G26,2,FALSE)</f>
         <v>7</v>
       </c>
-      <c r="I10" s="11">
-        <f>H10/Total_Terminations</f>
+      <c r="I10" s="10">
+        <f t="shared" si="2"/>
         <v>6.7307692307692304E-2</v>
       </c>
       <c r="K10" s="2" t="str">
@@ -54255,8 +54271,8 @@
         <f>VLOOKUP('Attrition Analysis'!K13,'Pivot Tables'!$I$4:$K$24,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="N10" s="11">
-        <f>M10/L10</f>
+      <c r="N10" s="10">
+        <f t="shared" si="3"/>
         <v>0.31578947368421051</v>
       </c>
     </row>
@@ -54285,24 +54301,24 @@
         <f>VLOOKUP(G11,'Pivot Tables'!F10:G27,2,FALSE)</f>
         <v>5</v>
       </c>
-      <c r="I11" s="11">
-        <f>H11/Total_Terminations</f>
+      <c r="I11" s="10">
+        <f t="shared" si="2"/>
         <v>4.807692307692308E-2</v>
       </c>
-      <c r="K11" s="12" t="str">
+      <c r="K11" s="11" t="str">
         <f>INDEX('Pivot Tables'!I10:I30,1,1)</f>
         <v>David Stanley</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="11">
         <f>VLOOKUP(K11,'Pivot Tables'!$I$4:$K$24,2,FALSE)</f>
         <v>21</v>
       </c>
-      <c r="M11" s="12">
+      <c r="M11" s="11">
         <f>VLOOKUP('Attrition Analysis'!K10,'Pivot Tables'!$I$4:$K$24,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="N11" s="13">
-        <f>M11/L11</f>
+      <c r="N11" s="12">
+        <f t="shared" si="3"/>
         <v>0.2857142857142857</v>
       </c>
     </row>
@@ -54315,8 +54331,8 @@
         <f>VLOOKUP(G12,'Pivot Tables'!F11:G28,2,FALSE)</f>
         <v>5</v>
       </c>
-      <c r="I12" s="11">
-        <f>H12/Total_Terminations</f>
+      <c r="I12" s="10">
+        <f t="shared" si="2"/>
         <v>4.807692307692308E-2</v>
       </c>
       <c r="K12" s="2" t="str">
@@ -54331,8 +54347,8 @@
         <f>VLOOKUP('Attrition Analysis'!K11,'Pivot Tables'!$I$4:$K$24,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="N12" s="11">
-        <f>M12/L12</f>
+      <c r="N12" s="10">
+        <f t="shared" si="3"/>
         <v>0.27272727272727271</v>
       </c>
     </row>
@@ -54345,24 +54361,24 @@
         <f>VLOOKUP(G13,'Pivot Tables'!F12:G29,2,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="I13" s="11">
-        <f>H13/Total_Terminations</f>
+      <c r="I13" s="10">
+        <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="K13" s="12" t="str">
+      <c r="K13" s="11" t="str">
         <f>INDEX('Pivot Tables'!I12:I32,1,1)</f>
         <v>Brannon Miller</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="11">
         <f>VLOOKUP(K13,'Pivot Tables'!$I$4:$K$24,2,FALSE)</f>
         <v>22</v>
       </c>
-      <c r="M13" s="12">
+      <c r="M13" s="11">
         <f>VLOOKUP('Attrition Analysis'!K12,'Pivot Tables'!$I$4:$K$24,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="N13" s="13">
-        <f>M13/L13</f>
+      <c r="N13" s="12">
+        <f t="shared" si="3"/>
         <v>0.27272727272727271</v>
       </c>
     </row>
@@ -54375,8 +54391,8 @@
         <f>VLOOKUP(G14,'Pivot Tables'!F13:G30,2,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="I14" s="11">
-        <f>H14/Total_Terminations</f>
+      <c r="I14" s="10">
+        <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
     </row>
